--- a/sheets/국악이꽃피는나무/검수/산조의 기교.xlsx
+++ b/sheets/국악이꽃피는나무/검수/산조의 기교.xlsx
@@ -1750,20 +1750,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="43.01" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="63.87" customHeight="true">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="63.87" customHeight="true">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="63.87" customHeight="true">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="I5" s="24"/>
     </row>
-    <row r="6" ht="63.87" customHeight="true">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="63.87" customHeight="true">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" ht="63.87" customHeight="true">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" ht="63.87" customHeight="true">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" ht="63.87" customHeight="true">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" ht="63.87" customHeight="true">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I11" s="24"/>
     </row>
-    <row r="12" ht="63.87" customHeight="true">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="63.87" customHeight="true">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="63.87" customHeight="true">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -2072,6 +2072,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>